--- a/metadata/ECRMDP_Source_to_Target_Mapping.xlsx
+++ b/metadata/ECRMDP_Source_to_Target_Mapping.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Bronze_Mapping!$A$1:$I$98</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Key_Lookups!$A$1:$G$22</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Open_Issues!$A$1:$G$10</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Open_Issues!$A$1:$G$11</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Source_Inventory!$A$1:$H$12</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Warehouse_Mapping!$A$1:$I$135</definedName>
   </definedNames>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2426" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="386">
   <si>
     <t xml:space="preserve">ECRMDP - Source-to-Target Mapping (UC16, Sprint 3)</t>
   </si>
@@ -1174,16 +1174,22 @@
     <t xml:space="preserve">silver/cleansing/data_cleaning.py</t>
   </si>
   <si>
-    <t xml:space="preserve">Reads raw files from ../Datasets/customer_360_mixed_formats/, which is not in the repo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silver files cannot be regenerated from the repo alone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Point the script at datasets/ to make it reproducible.</t>
+    <t xml:space="preserve">Read raw files from ../Datasets/customer_360_mixed_formats/, which is not in the repo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silver files could not be regenerated from the repo alone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Script now reads and writes datasets/ in the repo; it reproduces 9 of 10 silver files byte-for-byte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleansing Title Case turned UK/USA into 'Uk'/'Usa' (raw data has UK/USA).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same country shown twice in cross-source country filters.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acronyms restored in data_cleaning.py; 559 customer rows corrected.</t>
   </si>
 </sst>
 </file>
@@ -1259,7 +1265,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1299,12 +1305,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
-        <bgColor rgb="FFE7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
@@ -1358,7 +1358,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1423,10 +1423,6 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1436,7 +1432,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1487,14 +1483,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFDDEBF7"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFFCE4D6"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -1522,7 +1510,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFCE4D6"/>
-      <rgbColor rgb="FFDDEBF7"/>
+      <rgbColor rgb="FFE7E6E6"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -1536,7 +1524,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFE7E6E6"/>
+      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFFFE699"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -9630,7 +9618,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -9865,15 +9853,38 @@
       <c r="E10" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="G10" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="G10" s="11" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>383</v>
       </c>
+      <c r="E11" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>385</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G11"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
